--- a/2026_10/2026_10_05/pet/Pet_Report_template.xlsx
+++ b/2026_10/2026_10_05/pet/Pet_Report_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenalee\work\2026_09\2026_10\2026_10_05\pet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9C384E-F054-4DD3-98DD-7C07E116FC23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15686971-D6B0-4D68-82B7-66702395EF42}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="11460" xr2:uid="{99FE362A-8639-4739-B307-EA460C1472ED}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="11460" activeTab="1" xr2:uid="{99FE362A-8639-4739-B307-EA460C1472ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Navigation" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="21">
   <si>
     <t>APP</t>
   </si>
@@ -41,18 +41,6 @@
   </si>
   <si>
     <t>view.SR1.Promotion | CityID:0;PromotionId:100;Sn:https://www.openrice.com/zh/hongkong/restaurants?sortBy=ORScoreDesc&amp;conditionId=11024&amp;tabIndex=0</t>
-  </si>
-  <si>
-    <t>11:53:37|| or.search.quick| CityID:0;AmtID:20232;Page:1;Lang:zh_TW;Ver:7.21.0; sn:hk.QckSearch</t>
-  </si>
-  <si>
-    <t>11:53:37|| view.SR1.Promotion| CityID:0;PromotionID:100;;Lang:zh_TW;Ver:7.21.0; sn:hk.Search.SR1.1</t>
-  </si>
-  <si>
-    <t>11:54:44|| or.search.adv| CityID:0;SortBy:orscoredesc;Page:1;FeatureFlt:11024;Lang:zh_TW;Ver:7.21.0; sn:hk.AdvSearch</t>
-  </si>
-  <si>
-    <t>11:54:44|| view.SR1.Promotion| CityID:0;PromotionID:100;;Lang:zh_TW;Ver:7.21.0; sn:hk.Search.SR1.1</t>
   </si>
   <si>
     <t>:</t>
@@ -102,6 +90,284 @@
       <t>Adv Search</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>view.SR1.Promotion | CityID:0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PromotionId:100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;Sn:https://www.openrice.com/zh/hongkong/restaurants?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amenityId=20232</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;tabIndex=0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>or.search.adv | CityID:0;Sr:Biz;SortBy:ORScoreDesc;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ConditionId:11024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;UiCity:hongkong;Sn:https://www.openrice.com/zh/hongkong/restaurants?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>amenityId=20232</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;tabIndex=0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11:53:37|| or.search.quick| CityID:0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AmtID:20232</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;Page:1;Lang:zh_TW;Ver:7.21.0; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sn:hk.QckSearch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11:53:37|| view.SR1.Promotion| CityID:0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PromotionID:100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;;Lang:zh_TW;Ver:7.21.0; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sn:hk.Search.SR1.1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11:54:44|| or.search.adv| CityID:0;SortBy:orscoredesc;Page:1;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FeatureFlt:11024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;Lang:zh_TW;Ver:7.21.0; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sn:hk.AdvSearch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>11:54:44|| view.SR1.Promotion| CityID:0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PromotionID:100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">;;Lang:zh_TW;Ver:7.21.0; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sn:hk.Search.SR1.1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>view.SR1.Promotion | CityID:0;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PromotionId:100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;Sn:https://www.openrice.com/zh/hongkong/restaurants?sortBy=ORScoreDesc&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>conditionId=11024</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;tabIndex=0</t>
+    </r>
+  </si>
+  <si>
+    <t>ios</t>
+  </si>
 </sst>
 </file>
 
@@ -110,7 +376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,8 +403,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +433,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -294,18 +573,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -317,6 +584,19 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +793,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>363286</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -623,7 +903,7 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -667,7 +947,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>65677</xdr:rowOff>
+      <xdr:rowOff>56152</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -704,13 +984,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>119854</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1139,346 +1419,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>15</v>
+      <c r="A1" s="24" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>14</v>
+      <c r="C2" s="25" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>16</v>
+      <c r="A36" s="24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="29" t="s">
+      <c r="A37" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="29" t="s">
-        <v>14</v>
+      <c r="C37" s="25" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="30"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="30"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
+      <c r="A50" s="26"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
+      <c r="A52" s="26"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="30"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
+      <c r="A56" s="26"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="31"/>
+      <c r="A57" s="26"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="30"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
+      <c r="A59" s="26"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
+      <c r="A60" s="26"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="30"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="30"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
+      <c r="A62" s="26"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
+      <c r="A63" s="26"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="30"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
+      <c r="A64" s="26"/>
+      <c r="B64" s="27"/>
+      <c r="C64" s="27"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="31"/>
+      <c r="A65" s="26"/>
+      <c r="B65" s="27"/>
+      <c r="C65" s="27"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="30"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="30"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
+      <c r="A67" s="26"/>
+      <c r="B67" s="27"/>
+      <c r="C67" s="27"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="32"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
+      <c r="A68" s="28"/>
+      <c r="B68" s="27"/>
+      <c r="C68" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1487,125 +1767,161 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E6126D-B16D-4F43-87F0-FC7D5C28387D}">
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:AA82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="O6" s="22"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L7" s="26" t="s">
+      <c r="M6" s="22"/>
+      <c r="N6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="31"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="L7" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="26" t="s">
-        <v>12</v>
+      <c r="M7" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M8" s="26"/>
-      <c r="N8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M8" s="22"/>
+      <c r="N8" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="33"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M9" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M10" s="22"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="L12" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M13" s="22"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M14" s="22"/>
+    </row>
+    <row r="17" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="N17" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" s="30"/>
+    </row>
+    <row r="18" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="L18" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="M19" s="22"/>
+      <c r="N19" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="33"/>
+    </row>
+    <row r="20" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="M20" s="22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="L21" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="12:27" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D34" s="31" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M9" s="26"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L10" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" s="26"/>
-      <c r="N10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M11" s="26"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M12" s="26"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N15" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="O15" s="23"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L16" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="M16" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="E34" s="31"/>
+      <c r="H34" s="30" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="M17" s="26"/>
-      <c r="N17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="M18" s="26"/>
-    </row>
-    <row r="19" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="L19" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="M19" s="26"/>
-      <c r="N19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="12:14" x14ac:dyDescent="0.25">
-      <c r="N20" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D34" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="H34" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="23"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
@@ -1622,10 +1938,8 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="14"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="15"/>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
@@ -1636,8 +1950,6 @@
       <c r="I39" s="16"/>
       <c r="J39" s="16"/>
       <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="17"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B40" s="15"/>
@@ -1650,8 +1962,8 @@
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
       <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="17"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="14"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B41" s="15"/>
@@ -1765,7 +2077,7 @@
       <c r="L48" s="16"/>
       <c r="M48" s="17"/>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B49" s="15"/>
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
@@ -1778,12 +2090,8 @@
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="17"/>
-      <c r="O49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="P49" s="24"/>
-    </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B50" s="15"/>
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
@@ -1796,10 +2104,8 @@
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="17"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="24"/>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="15"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
@@ -1812,8 +2118,12 @@
       <c r="K51" s="16"/>
       <c r="L51" s="16"/>
       <c r="M51" s="17"/>
-    </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O51" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="P51" s="32"/>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="15"/>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
@@ -1826,8 +2136,10 @@
       <c r="K52" s="16"/>
       <c r="L52" s="16"/>
       <c r="M52" s="17"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" s="15"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
@@ -1841,7 +2153,7 @@
       <c r="L53" s="16"/>
       <c r="M53" s="17"/>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" s="15"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -1855,7 +2167,7 @@
       <c r="L54" s="16"/>
       <c r="M54" s="17"/>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -1869,7 +2181,7 @@
       <c r="L55" s="16"/>
       <c r="M55" s="17"/>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -1883,7 +2195,7 @@
       <c r="L56" s="16"/>
       <c r="M56" s="17"/>
     </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B57" s="15"/>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -1897,7 +2209,7 @@
       <c r="L57" s="16"/>
       <c r="M57" s="17"/>
     </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="15"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
@@ -1911,7 +2223,7 @@
       <c r="L58" s="16"/>
       <c r="M58" s="17"/>
     </row>
-    <row r="59" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="18"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
@@ -1922,16 +2234,22 @@
       <c r="I59" s="19"/>
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
-      <c r="L59" s="19"/>
-      <c r="M59" s="20"/>
-    </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="L59" s="16"/>
+      <c r="M59" s="17"/>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L60" s="16"/>
+      <c r="M60" s="17"/>
+    </row>
+    <row r="61" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L61" s="19"/>
+      <c r="M61" s="20"/>
+    </row>
+    <row r="62" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -1942,10 +2260,8 @@
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-    </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="6"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
@@ -1956,18 +2272,8 @@
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="6"/>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
@@ -1978,16 +2284,8 @@
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
-      <c r="N65" s="7"/>
-      <c r="O65" s="7"/>
-      <c r="P65" s="7"/>
-      <c r="Q65" s="8"/>
-      <c r="R65" s="7"/>
-      <c r="S65" s="7"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="7"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
     </row>
     <row r="66" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B66" s="6"/>
@@ -2002,10 +2300,10 @@
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
-      <c r="N66" s="7"/>
-      <c r="O66" s="7"/>
-      <c r="P66" s="7"/>
-      <c r="Q66" s="8"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="5"/>
       <c r="R66" s="7"/>
       <c r="S66" s="7"/>
       <c r="T66" s="7"/>
@@ -2095,10 +2393,8 @@
       <c r="P70" s="7"/>
       <c r="Q70" s="8"/>
       <c r="R70" s="7"/>
-      <c r="S70" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="T70" s="25"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
       <c r="U70" s="7"/>
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
@@ -2119,8 +2415,8 @@
       <c r="P71" s="7"/>
       <c r="Q71" s="8"/>
       <c r="R71" s="7"/>
-      <c r="S71" s="25"/>
-      <c r="T71" s="25"/>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
       <c r="U71" s="7"/>
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.25">
@@ -2141,8 +2437,10 @@
       <c r="P72" s="7"/>
       <c r="Q72" s="8"/>
       <c r="R72" s="7"/>
-      <c r="S72" s="7"/>
-      <c r="T72" s="7"/>
+      <c r="S72" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="T72" s="29"/>
       <c r="U72" s="7"/>
     </row>
     <row r="73" spans="2:21" x14ac:dyDescent="0.25">
@@ -2163,8 +2461,8 @@
       <c r="P73" s="7"/>
       <c r="Q73" s="8"/>
       <c r="R73" s="7"/>
-      <c r="S73" s="7"/>
-      <c r="T73" s="7"/>
+      <c r="S73" s="29"/>
+      <c r="T73" s="29"/>
       <c r="U73" s="7"/>
     </row>
     <row r="74" spans="2:21" x14ac:dyDescent="0.25">
@@ -2266,8 +2564,8 @@
       <c r="I78" s="10"/>
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
+      <c r="L78" s="7"/>
+      <c r="M78" s="7"/>
       <c r="N78" s="7"/>
       <c r="O78" s="7"/>
       <c r="P78" s="7"/>
@@ -2277,7 +2575,7 @@
       <c r="T78" s="7"/>
       <c r="U78" s="7"/>
     </row>
-    <row r="79" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -2290,41 +2588,63 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="11"/>
+      <c r="N79" s="7"/>
+      <c r="O79" s="7"/>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="8"/>
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>3</v>
       </c>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
       <c r="N80" s="7"/>
       <c r="O80" s="7"/>
       <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
+      <c r="Q80" s="8"/>
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
       <c r="T80" s="7"/>
       <c r="U80" s="7"/>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>4</v>
       </c>
+      <c r="L81" s="7"/>
+      <c r="M81" s="7"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="10"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="11"/>
+      <c r="R81" s="7"/>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7"/>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.25">
+      <c r="N82" s="7"/>
+      <c r="O82" s="7"/>
+      <c r="P82" s="7"/>
+      <c r="Q82" s="7"/>
+      <c r="R82" s="7"/>
+      <c r="S82" s="7"/>
+      <c r="T82" s="7"/>
+      <c r="U82" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="S70:T71"/>
+    <mergeCell ref="S72:T73"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="O49:P50"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="O51:P52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
